--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_07_Data Foundations, Embedding _ Vector Store/Day_07_Phan_03_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_07_Data Foundations, Embedding _ Vector Store/Day_07_Phan_03_21_Cau.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>60</v>
@@ -683,7 +683,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xét xem email và số điện thoại còn xuất hiện trước khi embeddings được tạo.</t>
+          <t>Vector embeddings không có tính chất tự động ẩn danh hóa dữ liệu cá nhân (PII như email, số điện thoại) vì kẻ tấn công có thể thực hiện tấn công nghịch đảo embedding (inversion attacks) để tái dựng văn bản gốc. Bắt buộc phải thực hiện khử định danh (redaction/masking) trước khi tạo embeddings.</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>60</v>
@@ -728,7 +728,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm riêng `doc_id`, URL nguồn và tập giá trị được phép của `department`.</t>
+          <t>Bản ghi metadata chuẩn hóa và tin cậy cho RAG phải chứa đầy đủ: `doc_id` duy nhất, URL gốc nguồn sự thật, thời điểm thu thập (timestamp), phiên bản tài liệu, thẩm quyền ban hành, và các thuộc tính nghiệp vụ (như `department`) tuân thủ tập giá trị cho phép (controlled vocabulary).</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>60</v>
@@ -985,7 +985,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mô hình, cách chuẩn hóa và thước đo phải khớp ở cả tài liệu lẫn truy vấn.</t>
+          <t>Lựa chọn ít rủi ro nhất khi quản trị kho vector: giữ mô hình, phương pháp chuẩn hóa L2 và thước đo cosine tương thích trên cả kho tài liệu lẫn truy vấn; khi chuyển đổi sang mô hình mới bắt buộc phải re-embed và re-index toàn bộ dữ liệu. Không được trộn thô vector khác mô hình.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>60</v>
@@ -1193,7 +1193,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đặt câu hỏi: hai nội dung khác nhau có được phép dùng cùng một danh tính ổn định hay không?</t>
+          <t>Khi kho tài liệu đã có bản ghi `A::0` và bản ghi mới cùng `record_id=A::0` nhưng nội dung khác nhau, đồng thời quy ước hệ thống cấm ghi đè ngầm (silent overwrite): hệ thống phải từ chối hoặc báo lỗi xung đột định danh trước khi ghi vào kho, và chỉ cho phép cập nhật qua quy trình quản lý phiên bản rõ ràng.</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1238,7 +1238,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Muốn kiểm quy tắc đồng điểm, dữ liệu kiểm thử phải có đúng các điểm bằng nhau.</t>
+          <t>Để kiểm tra tính xác định của quy tắc phá hòa (tie-breaking) khi các bản ghi có điểm bằng nhau (ví dụ cùng 0,9), bộ dữ liệu kiểm thử phải tạo hai bản ghi có điểm bằng nhau nhưng đảo thứ tự ID, sau đó xác minh rằng hệ thống luôn xếp hạng theo thứ tự `record_id` tăng dần như quy ước.</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1283,7 +1283,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Lọc nhiều điều kiện dùng đồng thời tất cả điều kiện bắt buộc.</t>
+          <t>Lọc kết hợp hai điều kiện `department=engineering AND semester=2026`: một bản ghi chỉ khớp khi thỏa mãn đồng thời cả hai điều kiện. Bản ghi R thiếu trường `semester` nên không thỏa; chỉ có bản ghi S có đầy đủ cả hai giá trị hợp lệ mới khớp.</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1383,7 +1383,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dựa vào bằng chứng của từng bước, không đổi nhiều biến kiểm soát cùng lúc.</t>
+          <t>Khi tối ưu tham số k trong RAG: k=2 thiếu bằng chứng còn k=8 quá nhiều nhiễu. Khi giữ cố định ngưỡng và bộ lọc, bước tiếp theo đúng phương pháp khoa học là so sánh các giá trị k trung gian (k=2, 3, 4) trên cùng một bộ truy vấn đóng băng và đo lường độ bao phủ cùng tỷ lệ trùng lặp.</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.964</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1597,7 +1597,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính DCG của xếp hạng thực tế và IDCG của xếp hạng lý tưởng trước khi chia.</t>
+          <t>Tính DCG@3 thực tế cho mức liên quan [2, 0, 1]: rank 1 = (2² - 1)/log₂(1+1) = 3/1 = 3; rank 2 = (2⁰ - 1)/log₂(2+1) = 0; rank 3 = (2¹ - 1)/log₂(3+1) = 1/2 = 0,5 =&gt; DCG@3 = 3 + 0 + 0,5 = 3,5. Xếp hạng lý tưởng [2, 1, 0]: rank 1 = 3; rank 2 = (2¹ - 1)/log₂(3) = 1/log₂(3) ≈ 0,6309298; rank 3 = 0 =&gt; IDCG@3 = 3 + 0,6309298 ≈ 3,6309298. NDCG@3 = DCG / IDCG = 3,5 / 3,6309298 ≈ 0,96394... Làm tròn ba chữ số thập phân là 0,964.</t>
         </is>
       </c>
     </row>
